--- a/crosswalk/xlsx/tennessee-history__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/tennessee-history__primary-source-crosswalk.xlsx
@@ -31,7 +31,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,16 +48,6 @@
         <fgColor rgb="00E6EFE4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6E9D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6DDD4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -71,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -80,12 +70,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -652,7 +636,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -694,42 +678,40 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>First Peoples: Paleoindian and Archaic artifacts (Tennessee State Museum)</t>
+          <t>Paleoindian and Archaic stone tools and projectile points from the Southeastern U.S. (Smithsonian Open Access, CC0)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>artifact/photograph</t>
+          <t>artifact photograph</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
+          <t>Smithsonian National Museum of Natural History, Department of Anthropology</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1930</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum (tnmuseum.org)</t>
+          <t>Smithsonian Institution (collections.si.edu)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Museum-held artifacts; verify individual image rights</t>
+          <t>Public domain / CC0 (filter results to Smithsonian Open Access, CC0)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://tnmuseum.org/search?q=Paleoindian%20Archaic%20artifacts</t>
+          <t>https://www.si.edu/search/collection-images?edan_q=Tennessee+Archaic+projectile+point&amp;edan_fq%5B0%5D=media_usage%3A%22CC0%22</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -739,32 +721,32 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum, First Peoples collection.</t>
+          <t>Chipped-stone projectile points and tools, Archaic period, Southeastern United States, Department of Anthropology, Smithsonian National Museum of Natural History, Smithsonian Open Access (CC0).</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Paleoindian and Archaic stone artifacts excavated in Tennessee.</t>
+          <t>Fluted and stemmed chipped-stone projectile points and hafted tools from the Paleoindian and Archaic periods, showing the hunting technology of the region's earliest peoples.</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.05</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Alternate context source; image rights vary by object—verify before commercial reuse.</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Replaces rights-uncertain TN State Museum images with Smithsonian Open Access artifacts released CC0 (genuinely commercial-use safe). Teacher should filter the results to the CC0 media-usage facet. The artifacts themselves are millennia old (PD by age); CC0 clears the photograph rights too. Directly supports late-ice-age-through-Archaic life in the region.</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -846,7 +828,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -888,42 +870,40 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mississippian stone effigy statues and shell gorgets from Tennessee</t>
+          <t>Engraved shell gorgets of the Mississippian Southeast (Holmes, 'Art in Shell of the Ancient Americans,' 2nd Annual Report, Bureau of Ethnology)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>artifact/photograph</t>
+          <t>illustrated government report (plates)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum / Frank H. McClung Museum</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>c. 1000-1500 CE</t>
-        </is>
+          <t>William Henry Holmes, Bureau of Ethnology, Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1883</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum (tnmuseum.org)</t>
+          <t>Smithsonian Institution / Bureau of American Ethnology (via si.edu; also HathiTrust)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Museum-held artifacts; verify image rights</t>
+          <t>Public domain (U.S. government publication, published 1883)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://tnmuseum.org/search?q=Mississippian%20stone%20statue%20shell%20gorget</t>
+          <t>https://library.si.edu/digital-library/search?edan_q=Holmes+Art+in+Shell+Ancient+Americans</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -933,32 +913,32 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Museum, Mississippian collection (stone effigy figures, engraved shell gorgets).</t>
+          <t>William H. Holmes, "Art in Shell of the Ancient Americans," Second Annual Report of the Bureau of Ethnology to the Secretary of the Smithsonian Institution, 1880-81 (Washington: GPO, 1883), engraved shell gorget plates.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kneeling Mississippian stone effigy statues and engraved marine-shell gorgets from Tennessee mound sites.</t>
+          <t>Nineteenth-century engraved plates depicting Mississippian-period marine-shell gorgets incised with spider, rattlesnake, and cross motifs excavated from Tennessee-region mounds.</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.05</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Iconic Mississippian material culture; image rights vary.</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>PD by age (1883 U.S. government publication) and depicts the very Mississippian shell-gorget and effigy artwork the standard names, replacing the rights-uncertain State Museum photos. Cyrus Thomas's 1894 'Report on the Mound Explorations of the Bureau of Ethnology' (12th Annual Report) is an equally PD companion covering Tennessee mounds.</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1020,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1137,7 +1117,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1234,7 +1214,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1331,7 +1311,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1428,7 +1408,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1525,7 +1505,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1622,7 +1602,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1664,42 +1644,40 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Records and images of Fort Loudoun (British fort, 1756-1760)</t>
+          <t>Henry Timberlake, 'A Draught of the Cherokee Country' (1765 map of the Overhill Cherokee towns and the Little Tennessee valley)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>document/photograph</t>
+          <t>map</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1756-1760</t>
-        </is>
+          <t>Lt. Henry Timberlake</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1765</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Library of Congress (loc.gov)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; historical records often PD</t>
+          <t>Public domain (published 1765)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Fort%20Loudoun</t>
+          <t>https://www.loc.gov/search/?q=Timberlake+Draught+of+the+Cherokee+Country</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1709,17 +1687,17 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive, Fort Loudoun materials.</t>
+          <t>Henry Timberlake, A Draught of the Cherokee Country... (London, 1765), Geography and Map Division, Library of Congress.</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Documents and site images relating to British Fort Loudoun in the Overhill Cherokee country.</t>
+          <t>A 1765 manuscript-style map of the Overhill Cherokee towns along the Little Tennessee River near Fort Loudoun, drawn by British Lieutenant Henry Timberlake.</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1729,12 +1707,12 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Fort Loudoun illustrates the imperial contest on the Tennessee frontier.</t>
-        </is>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>PD by age and geographically precise to the Fort Loudoun / Overhill Cherokee contest zone of the 1750s-60s, replacing the rights-uncertain TeVA Fort Loudoun images. A National Park Service page on Fort Loudoun offers a PD federal alternative if a period map is not preferred.</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1794,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1913,7 +1891,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2010,7 +1988,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2107,7 +2085,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2204,7 +2182,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2301,7 +2279,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2398,7 +2376,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2495,7 +2473,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2592,7 +2570,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2689,7 +2667,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2782,7 +2760,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2875,7 +2853,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2968,7 +2946,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3061,7 +3039,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3158,7 +3136,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3255,7 +3233,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3352,7 +3330,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3449,7 +3427,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3487,42 +3465,40 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Photographs and sketches of early Tennessee farm and community life</t>
+          <t>Historic American Buildings Survey (HABS) documentation of early Tennessee log farmsteads and dwellings</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>photograph/illustration</t>
+          <t>measured drawings and documentary photographs</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>19th c.</t>
-        </is>
+          <t>Historic American Buildings Survey, National Park Service</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1934</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Library of Congress / National Park Service (loc.gov HABS collection)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; pre-1929 items PD</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/early%20Tennessee%20farm%20life%20frontier%20cabin</t>
+          <t>https://www.loc.gov/collections/historic-american-buildings-landscapes-and-engineering-records/?q=Tennessee+log+house+farm</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3532,17 +3508,17 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TSLA/TeVA, early Tennessee rural life images.</t>
+          <t>Historic American Buildings Survey, log dwellings and farm outbuildings, Tennessee, Prints and Photographs Division, Library of Congress (HABS).</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Images of log cabins, farms, and community gatherings in early Tennessee.</t>
+          <t>HABS measured drawings and photographs of an early Tennessee log farmhouse, barn, and outbuildings documenting frontier-era rural family life and work.</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3552,12 +3528,12 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Primary sources for daily farm/religion/community life were moderately hard to find; TeVA search recommended.</t>
-        </is>
-      </c>
-      <c r="S32" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Photography did not exist in the 1796-1812 period, so the honest PD substitute is federal HABS documentation of surviving early-Tennessee log farmsteads (public domain federal work). It supports the farm-life/work/community standard with buildable, rights-clean material, replacing rights-uncertain TeVA photos and sketches.</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3611,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3728,7 +3704,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3821,7 +3797,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3918,7 +3894,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4015,7 +3991,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4112,7 +4088,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4209,7 +4185,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4306,7 +4282,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4403,7 +4379,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4500,7 +4476,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4597,7 +4573,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4690,7 +4666,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4783,7 +4759,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4880,7 +4856,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4977,7 +4953,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5070,7 +5046,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5163,7 +5139,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5256,7 +5232,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5349,7 +5325,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5446,7 +5422,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5543,7 +5519,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5640,7 +5616,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5682,42 +5658,40 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Free Hill / Free Hills community records and imagery (Clay County)</t>
+          <t>Frances Wright, 'Explanatory Notes Respecting the Nature and Objects of the Institution of Nashoba' (and related Nashoba writings)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>document/photograph</t>
+          <t>printed pamphlet / primary document</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>19th-20th c.</t>
-        </is>
+          <t>Frances (Fanny) Wright</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1830</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>HathiTrust Digital Library / Library of Congress (public-domain works)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Verify per item</t>
+          <t>Public domain (published c. 1828-1830)</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Free%20Hill%20freed%20slaves%20community</t>
+          <t>https://catalog.hathitrust.org/Search/Home?lookfor=Frances+Wright+Nashoba&amp;type=all</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -5727,32 +5701,32 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>TeVA, Free Hill/Free Hills community materials.</t>
+          <t>Frances Wright, Explanatory Notes Respecting the Nature and Objects of the Institution of Nashoba (New-Harmony, Ind., 1830).</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Records and images of the Free Hill settlement of freed African Americans.</t>
+          <t>Printed pages of Frances Wright's own explanation of the Nashoba community near Memphis, her experimental settlement intended to prepare enslaved people for emancipation.</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Primary material for Free Hill was hard to find; TeVA search recommended, verify rights.</t>
-        </is>
-      </c>
-      <c r="S55" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The standard pairs Nashoba with Free Hill; Free Hill (Clay County) has essentially no clean PD documentary primary source, so this anchors on the Nashoba half with Frances Wright's own PD writings (published c.1830), replacing rights-uncertain TeVA Free Hill records. Genuinely PD by age.</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5808,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5931,7 +5905,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6028,7 +6002,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6125,7 +6099,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6218,7 +6192,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6311,7 +6285,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -6408,7 +6382,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6505,7 +6479,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6598,7 +6572,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6691,7 +6665,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -6784,7 +6758,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6877,7 +6851,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -6970,7 +6944,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7063,7 +7037,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -7156,7 +7130,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -7249,7 +7223,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7287,42 +7261,40 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Portrait of Sampson W. Keeble, first Black Tennessee legislator (1873)</t>
+          <t>House Journal of the Thirty-Eighth General Assembly of the State of Tennessee (1873) — session in which Sampson W. Keeble served</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>portrait/document</t>
+          <t>official legislative record</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
+          <t>Tennessee General Assembly</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1873</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>HathiTrust / Tennessee State Library and Archives (tn.gov)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; pre-1929 likely PD</t>
+          <t>Public domain (state government edict / official record)</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Sampson%20Keeble%20legislator</t>
+          <t>https://catalog.hathitrust.org/Search/Home?lookfor=Tennessee+House+Journal+1873&amp;type=all</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -7332,32 +7304,32 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Sampson W. Keeble materials.</t>
+          <t>House Journal of the Thirty-Eighth General Assembly of the State of Tennessee, 1873, listing Representative Sampson W. Keeble of Davidson County.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Portrait and records of Sampson Keeble, elected to the Tennessee legislature in 1873.</t>
+          <t>Printed pages of the 1873 Tennessee House Journal recording the membership and proceedings of the General Assembly in which Sampson W. Keeble, the first African American elected to the Tennessee legislature, served.</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Named figure; primary images limited—verify rights before commercial use.</t>
-        </is>
-      </c>
-      <c r="S72" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Official state legislative journals are public-domain government records, replacing the rights-uncertain TeVA portrait. The 1873 House Journal is contemporaneous primary evidence of Keeble's election and service, directly documenting the standard's early Black lawmakers.</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7407,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7528,7 +7500,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7621,7 +7593,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7718,7 +7690,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7815,7 +7787,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7912,7 +7884,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -8009,7 +7981,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -8102,7 +8074,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -8195,7 +8167,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8292,7 +8264,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8389,7 +8361,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8431,42 +8403,40 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Photographs and reports of the Coal Creek War (Anderson County, 1891-1892)</t>
+          <t>Contemporary newspaper coverage of the Coal Creek War / convict-lease uprising, Anderson County, 1891-1892</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>photograph/document</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>1891-1892</t>
-        </is>
+          <t>Contemporary Tennessee and U.S. newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1892</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Chronicling America, Library of Congress (loc.gov)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; pre-1929 likely PD</t>
+          <t>Public domain (pre-1929 U.S. newspapers)</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Coal%20Creek%20War%20convict%20lease%20miners</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=Coal+Creek+miners+convict+lease+1892</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -8476,32 +8446,32 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Coal Creek War materials, 1891-1892.</t>
+          <t>Coverage of the Coal Creek troubles, Tennessee newspapers, 1891-1892, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Images of miners, militia, and stockades from the convict-lease uprising.</t>
+          <t>Front-page newspaper reporting from 1891-1892 on Anderson County miners revolting against the state's replacement of free labor with leased convicts at Coal Creek.</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Directly documents the Coal Creek Wars; verify item rights.</t>
-        </is>
-      </c>
-      <c r="S84" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1929 U.S. newspapers in Chronicling America are public domain. Contemporary 1891-92 reporting narrates the events and causes of the Coal Creek War directly, replacing rights-uncertain TeVA photos and reports.</t>
+        </is>
+      </c>
+      <c r="S84" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8553,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8676,7 +8646,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8769,7 +8739,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -8862,7 +8832,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -8955,7 +8925,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -9048,7 +9018,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -9141,7 +9111,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -9234,7 +9204,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -9272,42 +9242,40 @@
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Harry Burn / Anne Dallas Dudley suffrage materials (Tennessee)</t>
+          <t>Records and photographs of the 1920 Tennessee ratification of the 19th Amendment (National Woman's Party / suffrage collections)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>document/photograph</t>
+          <t>photographs and government ratification records</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>1918-1920</t>
-        </is>
+          <t>National Woman's Party; U.S. Government (records of ratification)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>1920</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Library of Congress (loc.gov); U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; 1920 materials likely PD</t>
+          <t>Public domain (pre-1929 images; U.S. federal ratification records)</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/suffrage%20Harry%20Burn%20Anne%20Dallas%20Dudley</t>
+          <t>https://www.loc.gov/search/?q=Tennessee+suffrage+ratification+nineteenth+amendment+1920</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -9317,32 +9285,32 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Tennessee suffrage collection (Burn, Dudley, ratification).</t>
+          <t>Tennessee ratification of the Nineteenth Amendment, August 1920; National Woman's Party Records / suffrage photographs, Library of Congress, and 19th Amendment ratification records, U.S. National Archives.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Photographs and documents of Tennessee suffrage leaders and the ratification vote.</t>
+          <t>1920 suffrage photographs and the federal record of Tennessee becoming the 'Perfect 36th' state to ratify the Nineteenth Amendment, the vote that secured women's suffrage.</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Named figures; the famous Febb Burn letter to Harry Burn is the key document. Verify rights.</t>
-        </is>
-      </c>
-      <c r="S93" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>1920 falls before the 1929 PD cutoff for the NWP suffrage photographs, and the ratification records are PD federal documents. This directly covers the 'Perfect 36,' Harry Burn, and Anne Dallas Dudley context while replacing rights-uncertain TeVA materials.</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9388,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9458,42 +9426,40 @@
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>WWI-era photographs of the Alcoa aluminum plant (Blount County, Tennessee)</t>
+          <t>Contemporary newspaper coverage of the Aluminum Company of America (Alcoa) plant and Blount County during World War I</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>various</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>1914-1920</t>
-        </is>
+          <t>Contemporary Tennessee newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1919</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Chronicling America, Library of Congress (loc.gov)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; pre-1929 likely PD</t>
+          <t>Public domain (pre-1929 U.S. newspapers)</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Alcoa%20aluminum%20plant%20Blount%20County%20World%20War</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=Alcoa+aluminum+Maryville+Tennessee+war</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -9503,32 +9469,32 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Alcoa plant photographs.</t>
+          <t>Coverage of the Alcoa aluminum works and wartime production, Tennessee newspapers, c. 1914-1919, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the Alcoa aluminum works that expanded during WWI.</t>
+          <t>World War I-era Tennessee newspaper reporting on the Aluminum Company of America plant and the boomtown of Alcoa in Blount County.</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Documents the Alcoa plant named in the standard; verify item rights.</t>
-        </is>
-      </c>
-      <c r="S95" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1929 newspapers are PD and keep the standard's Alcoa focus without rights-uncertain TeVA plant photos. For the standard's companion figure, Sgt. Alvin C. York's 1919 U.S. Army Signal Corps photograph and Medal of Honor records at NARA are an equally clean PD option.</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -9551,42 +9517,40 @@
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Governor Austin Peay portrait and messages to the General Assembly</t>
+          <t>Portrait of Governor Austin Peay (Harris &amp; Ewing) and his published messages to the Tennessee General Assembly</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>portrait/document</t>
+          <t>portrait photograph and official state messages</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives / Austin Peay</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>1923-1927</t>
-        </is>
+          <t>Harris &amp; Ewing (portrait); Governor Austin Peay (messages)</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1923</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Library of Congress (loc.gov, Harris &amp; Ewing Collection); HathiTrust for the messages</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; 1920s likely PD</t>
+          <t>Public domain (Harris &amp; Ewing pre-1929 collection; state government publications)</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Austin%20Peay%20governor%20messages</t>
+          <t>https://www.loc.gov/search/?q=Austin+Peay+Tennessee+governor+Harris+Ewing</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -9596,32 +9560,32 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Governor Austin Peay portrait and legislative messages, 1923-1927.</t>
+          <t>Austin Peay, Governor of Tennessee, Harris &amp; Ewing Collection, Prints and Photographs Division, Library of Congress; and Messages of Governor Austin Peay to the General Assembly (Nashville, 1923-1927).</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Portrait and official messages of Governor Austin Peay.</t>
+          <t>1920s photographic portrait of Tennessee Governor Austin Peay, whose administration reorganized state government and expanded roads and schools.</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Named figure; his messages document road-building and the 8-month school law. Verify rights.</t>
-        </is>
-      </c>
-      <c r="S96" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The Harris &amp; Ewing Collection at LoC is public domain and covers 1920s officials, and Peay's official gubernatorial messages are PD state publications documenting his infrastructure and education reforms, replacing the rights-uncertain TeVA portrait.</t>
+        </is>
+      </c>
+      <c r="S96" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9663,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -9792,7 +9756,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -9885,7 +9849,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -9982,7 +9946,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -10024,42 +9988,40 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the Grand Ole Opry / WSM and early country and blues performers</t>
+          <t>Contemporary newspaper coverage of WSM radio and the WSM Barn Dance / Grand Ole Opry founding, 1925-1927</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives / various</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>1920s-1940s</t>
-        </is>
+          <t>Contemporary Tennessee newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1927</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>Chronicling America, Library of Congress (loc.gov)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; some may be restricted</t>
+          <t>Public domain (pre-1929 U.S. newspapers)</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Grand%20Ole%20Opry%20WSM%20country%20music%20Nashville</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=WSM+radio+barn+dance+Nashville+1926</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -10069,32 +10031,32 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Grand Ole Opry / WSM photographs.</t>
+          <t>Coverage of WSM radio and the WSM Barn Dance (later Grand Ole Opry), Tennessee newspapers, 1925-1927, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the Grand Ole Opry, WSM radio, and early performers.</t>
+          <t>Mid-1920s Nashville newspaper coverage of WSM radio and its Barn Dance program, the broadcast that became the Grand Ole Opry.</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Covers the Opry/WSM/Carter Family/Bessie Smith side; verify item rights.</t>
-        </is>
-      </c>
-      <c r="S101" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The Opry's 1925-27 founding falls within the PD (pre-1929) newspaper window, so Chronicling America coverage of WSM and the Barn Dance replaces rights-uncertain TeVA photos while staying on the country-music development standard.</t>
+        </is>
+      </c>
+      <c r="S101" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10138,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10273,7 +10235,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10366,7 +10328,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10379,9 +10341,9 @@
           <t>Named innovator; patent is clean PD and directly on point.</t>
         </is>
       </c>
-      <c r="S104" s="5" t="inlineStr">
-        <is>
-          <t>REVIEW: repo unverified</t>
+      <c r="S104" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10421,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10472,9 +10434,9 @@
           <t>Named Nashville-raised innovator; patents are clean PD.</t>
         </is>
       </c>
-      <c r="S105" s="5" t="inlineStr">
-        <is>
-          <t>REVIEW: repo unverified</t>
+      <c r="S105" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10518,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -10653,7 +10615,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -10750,7 +10712,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -10847,7 +10809,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -10940,7 +10902,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -10978,42 +10940,40 @@
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Governor Frank Clement and Memphis boss Ed Crump</t>
+          <t>Hearings and reports of the U.S. Senate Special Committee to Investigate Organized Crime in Interstate Commerce (Kefauver Committee)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>congressional hearings / government report</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>1930s-1960s</t>
-        </is>
+          <t>U.S. Senate (Sen. Estes Kefauver, chairman)</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>1951</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>U.S. National Archives (archives.gov) / GPO (govinfo.gov)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; likely restricted</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Frank%20Clement%20Ed%20Crump%20governor%20politics</t>
+          <t>https://www.archives.gov/research/search?q=Kefauver+committee+organized+crime</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -11023,32 +10983,32 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Frank Clement and Ed Crump photographs.</t>
+          <t>U.S. Senate Special Committee to Investigate Organized Crime in Interstate Commerce (Kefauver Committee), Hearings and Final Report, 1950-1951, U.S. National Archives / GPO.</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Governor Frank Clement and political boss E.H. Crump.</t>
+          <t>Records of Tennessee Senator Estes Kefauver's nationally televised 1950-51 committee investigating organized crime, which made him a national figure.</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Named figures; mid-century photo rights vary—verify before commercial reuse.</t>
-        </is>
-      </c>
-      <c r="S111" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Federal records are PD. This anchors on the Kefauver Committee, unambiguously documenting one of the named 1950s-60s Tennesseans (Estes Kefauver), replacing rights-uncertain and copyrighted press photos of Clement/Crump/Memphis. Al Gore Sr.'s Congressional Record speeches are an additional PD option for the same standard.</t>
+        </is>
+      </c>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11071,42 +11031,40 @@
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the Nashville sit-ins and Diane Nash (1960)</t>
+          <t>U.S. Commission on Civil Rights report documenting Southern lunch-counter sit-ins and student nonviolent protest (1961)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>government report</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>various press / archives</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
+          <t>U.S. Commission on Civil Rights</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>1961</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / National Archives</t>
+          <t>U.S. Government Publishing Office (govinfo.gov) / U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; many press photos under copyright</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Nashville+sit-ins+1960+civil+rights+lunch+counter</t>
+          <t>https://www.archives.gov/research/search?q=Commission+on+Civil+Rights+1961+report+sit-ins</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -11116,32 +11074,32 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / NARA, Nashville sit-in photographs, 1960.</t>
+          <t>U.S. Commission on Civil Rights, Report (Washington: GPO, 1961), sections on student sit-in demonstrations and public-accommodations desegregation.</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the 1960 Nashville lunch-counter sit-in movement.</t>
+          <t>Federal civil-rights report from 1961 documenting the wave of student lunch-counter sit-ins, including the Nashville movement, and official responses to them.</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>Named topics; strong CLEAN-PD sit-in imagery is HARD to find—many are copyrighted press photos. Verify rights carefully.</t>
-        </is>
-      </c>
-      <c r="S112" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The famous Nashville sit-in and Diane Nash photographs are copyrighted press images with no clean PD equivalent; the honest PD substitute is the contemporaneous federal Commission on Civil Rights report (PD federal work), which documents the sit-in movement and fits the standard.</t>
+        </is>
+      </c>
+      <c r="S112" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11164,42 +11122,40 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the Clinton Twelve / Clinton High School desegregation (1956)</t>
+          <t>Federal court desegregation order in McSwain v. County Board of Education of Anderson County, Tennessee (1956)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>federal court record</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>various press / archives</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
+          <t>U.S. District Court for the Eastern District of Tennessee</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>1956</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; likely under copyright</t>
+          <t>Public domain (U.S. federal court record / government work)</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Clinton%20Twelve%20desegregation%201956%20Highlander</t>
+          <t>https://catalog.archives.gov/search?q=McSwain%20Anderson%20County%20Board%20of%20Education%20Clinton</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -11209,32 +11165,32 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Clinton desegregation and Highlander Folk School materials.</t>
+          <t>McSwain v. County Board of Education of Anderson County, Tennessee (E.D. Tenn., 1956), court order requiring desegregation of Clinton High School, Records of U.S. District Courts, National Archives.</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the 1956 Clinton High School desegregation and Highlander Folk School.</t>
+          <t>The 1956 federal court order desegregating Clinton High School, the legal action that opened the school to the twelve Black students known as the Clinton Twelve.</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Covers Clinton Twelve, Highlander, Tent City, Columbia. Rights vary; verify before reuse.</t>
-        </is>
-      </c>
-      <c r="S113" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The federal court order in McSwain is a public-domain government record that directly caused the desegregation of Clinton High School, providing a rights-clean primary source for the Clinton Twelve in place of rights-uncertain TeVA photographs.</t>
+        </is>
+      </c>
+      <c r="S113" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11257,42 +11213,40 @@
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Rev. James Lawson and the Nashville nonviolence workshops</t>
+          <t>U.S. Commission on Civil Rights records on Nashville and Tennessee desegregation and nonviolent protest</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>government report / records</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>various press / archives</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>1959-1961</t>
-        </is>
+          <t>U.S. Commission on Civil Rights</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>1961</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / TeVA</t>
+          <t>U.S. National Archives (archives.gov) / GPO (govinfo.gov)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; likely under copyright</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=James+Lawson+Nashville+nonviolence+civil+rights</t>
+          <t>https://www.archives.gov/research/search?q=Commission+on+Civil+Rights+Tennessee+Nashville</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -11302,32 +11256,32 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / TeVA, James Lawson and Nashville movement materials.</t>
+          <t>U.S. Commission on Civil Rights, reports and records on desegregation and nonviolent protest in Tennessee, c. 1959-1963, U.S. National Archives / GPO.</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Rev. James Lawson, architect of Nashville nonviolent protest.</t>
+          <t>Federal civil-rights records documenting Nashville's nonviolent desegregation movement, the setting for the workshops Rev. James Lawson led.</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>Named figures (Lawson, Kelly Miller Smith); clean-PD imagery HARD to find—verify rights.</t>
-        </is>
-      </c>
-      <c r="S114" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>No clean public-domain PHOTOGRAPH of James Lawson exists (press images are copyrighted). The best rights-clean primary is the PD federal Commission on Civil Rights record documenting the Nashville nonviolence movement Lawson trained. commercial_use_ok=true because the substitute is a federal document, but note that a Lawson portrait itself is not available PD.</t>
+        </is>
+      </c>
+      <c r="S114" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11350,42 +11304,40 @@
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Kelly Miller Smith and First Baptist Church Capitol Hill records</t>
+          <t>National Register of Historic Places nomination for First Baptist Church, Capitol Hill, Nashville</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>document/photograph</t>
+          <t>government documentation (NRHP nomination with photographs)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Tennessee State Library &amp; Archives / community archives</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>1950s-1960s</t>
-        </is>
+          <t>National Park Service (National Register of Historic Places)</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1972</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Tennessee Virtual Archive / TeVA</t>
+          <t>National Park Service (nps.gov) / U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Verify per item</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>https://teva.contentdm.oclc.org/digital/search/searchterm/Kelly%20Miller%20Smith%20First%20Baptist%20Capitol%20Hill</t>
+          <t>https://npgallery.nps.gov/NRHP/SearchResults?view=list&amp;q=First+Baptist+Church+Capitol+Hill+Nashville</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -11395,32 +11347,32 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>TeVA/TSLA, Kelly Miller Smith / First Baptist Capitol Hill materials.</t>
+          <t>First Baptist Church, Capitol Hill, Nashville, National Register of Historic Places Nomination Form, National Park Service.</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Records of Rev. Kelly Miller Smith and his Nashville congregation's civil-rights role.</t>
+          <t>Federal National Register documentation and photographs of First Baptist Church Capitol Hill, the Nashville congregation Rev. Kelly Miller Smith pastored and a hub of the civil rights movement.</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>Named figure; primary material limited—verify rights.</t>
-        </is>
-      </c>
-      <c r="S115" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>NRHP nomination forms and their documentary photographs are public-domain federal works. This documents First Baptist Church Capitol Hill, Kelly Miller Smith's church and a civil-rights movement center, giving a rights-clean primary in place of the rights-uncertain TeVA materials.</t>
+        </is>
+      </c>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11447,42 +11399,40 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>'I've Been to the Mountaintop' speech (Martin Luther King Jr., Memphis, April 3, 1968)</t>
+          <t>National Register of Historic Places nomination for the Lorraine Motel (National Civil Rights Museum site), Memphis</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>document/speech</t>
+          <t>government documentation (NRHP nomination with photographs)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Martin Luther King Jr.</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+          <t>National Park Service (National Register of Historic Places)</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1982</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / National Archives</t>
+          <t>National Park Service (nps.gov) / U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Under copyright (King estate) — cite/link only, do not reproduce commercially</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Martin+Luther+King+Memphis+1968+mountaintop+sanitation</t>
+          <t>https://npgallery.nps.gov/NRHP/SearchResults?view=list&amp;q=Lorraine+Motel+Memphis</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -11492,32 +11442,32 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Martin Luther King Jr., 'I've Been to the Mountaintop,' Memphis, April 3, 1968.</t>
+          <t>Lorraine Motel, Memphis, Tennessee, National Register of Historic Places Nomination Form, National Park Service.</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>MLK's final speech, delivered in Memphis during the sanitation workers' strike.</t>
+          <t>Federal National Register documentation and photographs of the Lorraine Motel in Memphis, site of Dr. Martin Luther King Jr.'s assassination and now the National Civil Rights Museum.</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>MLK speeches remain under copyright; clean-PD sources HARD. Use for reference/analysis, not commercial reproduction.</t>
-        </is>
-      </c>
-      <c r="S116" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Dr. King's 'I've Been to the Mountaintop' speech is under copyright (King estate) and is NOT available in the public domain; there is no clean PD version of the speech text or delivery. The rights-clean substitute is the PD federal NRHP documentation of the Lorraine Motel, which directly supports the standard's clause on the placement of the National Civil Rights Museum at that site.</t>
+        </is>
+      </c>
+      <c r="S116" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11544,42 +11494,40 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Photographs of the 1968 Memphis Sanitation Workers' Strike ('I AM A MAN')</t>
+          <t>Federal records of the 1968 Memphis sanitation workers' strike (Community Relations Service / Dept. of Labor mediation files)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>government records</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>various press photographers</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+          <t>U.S. Community Relations Service / U.S. Department of Labor</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>1968</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / National Archives</t>
+          <t>U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; many under copyright</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Memphis+sanitation+strike+1968+I+AM+A+MAN</t>
+          <t>https://catalog.archives.gov/search?q=Memphis%20sanitation%20strike%201968</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -11589,32 +11537,32 @@
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress / NARA, Memphis sanitation strike photographs, 1968.</t>
+          <t>Records relating to the 1968 Memphis sanitation workers' strike, U.S. Community Relations Service / Department of Labor, Records at the U.S. National Archives.</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Photographs of striking Memphis sanitation workers carrying 'I AM A MAN' placards.</t>
+          <t>Federal government records documenting the 1968 Memphis sanitation workers' strike and its mediation, the labor dispute that brought Dr. King to Memphis.</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.06</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Lorraine Motel/National Civil Rights Museum context. Many iconic images are copyrighted—verify rights.</t>
-        </is>
-      </c>
-      <c r="S117" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The iconic 'I AM A MAN' and strike photographs are copyrighted press images with no clean PD equivalent. The honest rights-clean primary is PD federal records on the strike and its federal mediation; commercial_use_ok=true covers the documents, but note that a PD period photograph of the strike is not available.</t>
+        </is>
+      </c>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11640,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -11785,7 +11733,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -11878,7 +11826,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -11971,7 +11919,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -12064,7 +12012,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -12102,42 +12050,40 @@
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Wilma Rudolph at the 1960 Rome Olympics</t>
+          <t>Congressional Record tribute honoring Wilma Rudolph (U.S. Congress)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>photograph</t>
+          <t>congressional record / government document</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>various (some U.S. government / news agency)</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1960</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>National Archives / Library of Congress</t>
+          <t>U.S. Government Publishing Office (govinfo.gov) / U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Verify per item; some PD, some restricted</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Wilma%20Rudolph%201960%20Olympics</t>
+          <t>https://www.govinfo.gov/app/search/%7B%22query%22%3A%22Wilma%20Rudolph%22%2C%22offset%22%3A0%7D</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -12147,32 +12093,32 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>National Archives / LOC, Wilma Rudolph Olympic photographs, 1960.</t>
+          <t>Tribute to Wilma Rudolph, Congressional Record, U.S. Congress (Washington: GPO), 1960s.</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Tennessee sprinter Wilma Rudolph winning three Olympic golds.</t>
+          <t>A public-domain Congressional Record tribute recognizing Clarksville, Tennessee, athlete Wilma Rudolph after her three gold medals at the 1960 Rome Olympics.</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Named figure; Alex Haley, Dolly Parton, Oprah imagery is copyrighted—prefer gov portraits. Verify rights.</t>
-        </is>
-      </c>
-      <c r="S123" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>The 1960 Rome Olympic photographs are copyrighted press/agency images with no clean PD equivalent. The rights-clean substitute is a PD Congressional Record tribute to Wilma Rudolph (federal document); commercial_use_ok=true for the document, but note that a PD photograph of Rudolph at the Rome Games is not available.</t>
+        </is>
+      </c>
+      <c r="S123" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12200,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12351,7 +12297,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -12444,7 +12390,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -12537,7 +12483,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -12630,7 +12576,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -12723,7 +12669,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
